--- a/Dobre_Ltd_AD_User_Provisioning_Input.xlsx
+++ b/Dobre_Ltd_AD_User_Provisioning_Input.xlsx
@@ -57,7 +57,7 @@
     <t>OUPath</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0001</t>
+    <t>DOB-2026-000001</t>
   </si>
   <si>
     <t>Daniel</t>
@@ -99,7 +99,7 @@
     <t>OU=Users,DC=dobre,DC=local</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0002</t>
+    <t>DOB-2026-000002</t>
   </si>
   <si>
     <t>Grace</t>
@@ -123,7 +123,7 @@
     <t>GG-FIN-REMOTE</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0003</t>
+    <t>DOB-2026-000003</t>
   </si>
   <si>
     <t>Patrick</t>
@@ -141,7 +141,7 @@
     <t>Douala</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0004</t>
+    <t>DOB-2026-000004</t>
   </si>
   <si>
     <t>Linda</t>
@@ -171,7 +171,7 @@
     <t>GG-HR-USERS</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0005</t>
+    <t>DOB-2026-000005</t>
   </si>
   <si>
     <t>Michael</t>
@@ -192,7 +192,7 @@
     <t>GG-HR-REMOTE</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0006</t>
+    <t>DOB-2026-000006</t>
   </si>
   <si>
     <t>Emmanuel</t>
@@ -222,7 +222,7 @@
     <t>GG-IT-ADMINS</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0007</t>
+    <t>DOB-2026-000007</t>
   </si>
   <si>
     <t>Sarah</t>
@@ -243,7 +243,7 @@
     <t>GG-IT-REMOTE</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0008</t>
+    <t>DOB-2026-000008</t>
   </si>
   <si>
     <t>John</t>
@@ -276,7 +276,7 @@
     <t>GG-SERVER-OPS</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0009</t>
+    <t>DOB-2026-000009</t>
   </si>
   <si>
     <t>Alice</t>
@@ -300,7 +300,7 @@
     <t>GG-SERVER-REMOTE-OPS</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0010</t>
+    <t>DOB-2026-000010</t>
   </si>
   <si>
     <t>Kevin</t>
@@ -318,7 +318,7 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0011</t>
+    <t>DOB-2026-000011</t>
   </si>
   <si>
     <t>Beatrice</t>
@@ -333,7 +333,7 @@
     <t>Accounts Payable Clerk</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0012</t>
+    <t>DOB-2026-000012</t>
   </si>
   <si>
     <t>Samuel</t>
@@ -348,7 +348,7 @@
     <t>HR Generalist</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0013</t>
+    <t>DOB-2026-000013</t>
   </si>
   <si>
     <t>Cynthia</t>
@@ -363,7 +363,7 @@
     <t>Help Desk Technician</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0014</t>
+    <t>DOB-2026-000014</t>
   </si>
   <si>
     <t>Derrick</t>
@@ -378,7 +378,7 @@
     <t>Backup Administrator</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0015</t>
+    <t>DOB-2026-000015</t>
   </si>
   <si>
     <t>Ruth</t>
@@ -396,7 +396,7 @@
     <t>United Kingdom</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0016</t>
+    <t>DOB-2026-000016</t>
   </si>
   <si>
     <t>Francis</t>
@@ -411,7 +411,7 @@
     <t>Accounts Receivable Clerk</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0017</t>
+    <t>DOB-2026-000017</t>
   </si>
   <si>
     <t>Miriam</t>
@@ -426,7 +426,7 @@
     <t>Budget Analyst</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0018</t>
+    <t>DOB-2026-000018</t>
   </si>
   <si>
     <t>George</t>
@@ -441,7 +441,7 @@
     <t>Payroll Officer</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0019</t>
+    <t>DOB-2026-000019</t>
   </si>
   <si>
     <t>Hilda</t>
@@ -456,7 +456,7 @@
     <t>Tax Compliance Officer</t>
   </si>
   <si>
-    <t>DOB-FIN-2025-0020</t>
+    <t>DOB-2026-000020</t>
   </si>
   <si>
     <t>Anthony</t>
@@ -471,7 +471,7 @@
     <t>Internal Auditor</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0021</t>
+    <t>DOB-2026-000021</t>
   </si>
   <si>
     <t>Peter</t>
@@ -486,7 +486,7 @@
     <t>HR Business Partner</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0022</t>
+    <t>DOB-2026-000022</t>
   </si>
   <si>
     <t>Comfort</t>
@@ -501,7 +501,7 @@
     <t>Talent Acquisition Lead</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0023</t>
+    <t>DOB-2026-000023</t>
   </si>
   <si>
     <t>Nelson</t>
@@ -516,7 +516,7 @@
     <t>Payroll &amp; Benefits Admin</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0024</t>
+    <t>DOB-2026-000024</t>
   </si>
   <si>
     <t>Ivy</t>
@@ -531,7 +531,7 @@
     <t>Training Coordinator</t>
   </si>
   <si>
-    <t>DOB-HRT-2025-0025</t>
+    <t>DOB-2026-000025</t>
   </si>
   <si>
     <t>Patience</t>
@@ -549,7 +549,7 @@
     <t>Kribi</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0026</t>
+    <t>DOB-2026-000026</t>
   </si>
   <si>
     <t>Bruno</t>
@@ -561,7 +561,7 @@
     <t>betonde</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0027</t>
+    <t>DOB-2026-000027</t>
   </si>
   <si>
     <t>Precious</t>
@@ -579,7 +579,7 @@
     <t>Germany</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0028</t>
+    <t>DOB-2026-000028</t>
   </si>
   <si>
     <t>Collins</t>
@@ -594,7 +594,7 @@
     <t>Network Administrator</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0029</t>
+    <t>DOB-2026-000029</t>
   </si>
   <si>
     <t>Faith</t>
@@ -615,7 +615,7 @@
     <t>Nigeria</t>
   </si>
   <si>
-    <t>DOB-ITX-2025-0030</t>
+    <t>DOB-2026-000030</t>
   </si>
   <si>
     <t>Roland</t>
@@ -627,7 +627,7 @@
     <t>IT Security Analyst</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0031</t>
+    <t>DOB-2026-000031</t>
   </si>
   <si>
     <t>Vincent</t>
@@ -642,7 +642,7 @@
     <t>Virtualization Engineer</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0032</t>
+    <t>DOB-2026-000032</t>
   </si>
   <si>
     <t>Diana</t>
@@ -660,7 +660,7 @@
     <t>South Africa</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0033</t>
+    <t>DOB-2026-000033</t>
   </si>
   <si>
     <t>Martin</t>
@@ -672,7 +672,7 @@
     <t>Storage Administrator</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0034</t>
+    <t>DOB-2026-000034</t>
   </si>
   <si>
     <t>Gloria</t>
@@ -693,7 +693,7 @@
     <t>France</t>
   </si>
   <si>
-    <t>DOB-SRV-2025-0035</t>
+    <t>DOB-2026-000035</t>
   </si>
   <si>
     <t>Judith</t>
@@ -830,7 +830,7 @@
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.6426982879639" customWidth="1"/>
+    <col min="1" max="1" width="17.6016826629639" customWidth="1"/>
     <col min="2" max="2" width="12.8876781463623" customWidth="1"/>
     <col min="3" max="3" width="12.5776891708374" customWidth="1"/>
     <col min="4" max="4" width="12.8518705368042" customWidth="1"/>
